--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487098_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487098_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9162</v>
+        <v>3.4905</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4612</v>
+        <v>3.5976</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4551</v>
+        <v>-0.1071</v>
       </c>
       <c r="G2" t="n">
         <v>3.069</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9426</v>
+        <v>0.5169</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1528</v>
+        <v>0.2892</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.2277</v>
       </c>
       <c r="V2" t="n">
         <v>2.4137</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.123</v>
+        <v>1.4621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8144</v>
+        <v>1.2338</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3086</v>
+        <v>0.2283</v>
       </c>
       <c r="G3" t="n">
         <v>3.6625</v>
@@ -688,13 +688,13 @@
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4237</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9227</v>
+        <v>-0.5033</v>
       </c>
       <c r="U3" t="n">
-        <v>0.499</v>
+        <v>0.4187</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5717</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0457</v>
+        <v>0.8443000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7184</v>
+        <v>-0.2883</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6728</v>
+        <v>1.1326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0364</v>
+        <v>-1.2763</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3973</v>
+        <v>0.2381</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3609</v>
+        <v>-1.5144</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0971</v>
+        <v>-0.2348</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0971</v>
+        <v>1.1332</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.368</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0607</v>
+        <v>-1.0415</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3002</v>
+        <v>-0.8951</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3609</v>
+        <v>-0.1464</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>1.9301</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>1.16</v>
+        <v>-1.0797</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5864</v>
+        <v>-0.3394</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4264</v>
+        <v>-0.7403</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0422</v>
+        <v>1.2702</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0422</v>
+        <v>0.9843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>A. RUIZ VICENTE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2583</v>
+        <v>0.5854</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7672</v>
+        <v>1.9848</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0256</v>
+        <v>-1.3994</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2763</v>
+        <v>1.4598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2381</v>
+        <v>3.1206</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5144</v>
+        <v>-1.6608</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2348</v>
+        <v>2.173</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1332</v>
+        <v>2.7271</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.368</v>
+        <v>-0.5541</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0415</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8951</v>
+        <v>0.3935</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1464</v>
+        <v>-1.1067</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9301</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6657</v>
+        <v>-0.7043</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8183</v>
+        <v>-0.158</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8474</v>
+        <v>-0.5463</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2702</v>
+        <v>-0.9421</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9843</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0829</v>
+        <v>0.4572</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8849</v>
+        <v>1.114</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8021</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9719</v>
+        <v>-2.529</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4032</v>
+        <v>-0.7668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4313</v>
+        <v>-1.7622</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1975</v>
+        <v>-0.8344</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.1075</v>
+        <v>-0.0519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.7825</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7744</v>
+        <v>-1.6946</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2956</v>
+        <v>-0.7149</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5212</v>
+        <v>-0.9797</v>
       </c>
       <c r="P6" t="n">
-        <v>0.772</v>
+        <v>1.7371</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0687</v>
+        <v>-0.5929</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3291</v>
+        <v>-0.1216</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2604</v>
+        <v>-0.4713</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1857</v>
+        <v>1.842</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1857</v>
+        <v>2.4559</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1475</v>
+        <v>0.2307</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.8766</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1475</v>
+        <v>-0.646</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.207</v>
+        <v>0.0364</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.207</v>
+        <v>1.3973</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.3609</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.0971</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.0971</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.207</v>
+        <v>-1.0607</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.207</v>
+        <v>0.3002</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-1.3609</v>
       </c>
       <c r="P7" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1335</v>
+        <v>0.345</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.7446</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1335</v>
+        <v>-0.3996</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RUIZ VICENTE</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5419</v>
+        <v>-0.0105</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2055</v>
+        <v>-1.8661</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7474</v>
+        <v>1.8556</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4598</v>
+        <v>-1.9719</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1206</v>
+        <v>-2.4032</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6608</v>
+        <v>0.4313</v>
       </c>
       <c r="J8" t="n">
-        <v>2.173</v>
+        <v>-1.1975</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7271</v>
+        <v>-1.1075</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5541</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.7744</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3935</v>
+        <v>-1.2956</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1067</v>
+        <v>0.5212</v>
       </c>
       <c r="P8" t="n">
         <v>0.772</v>
@@ -1078,28 +1078,28 @@
         <v>2.3161</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8316</v>
+        <v>0.0036</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9373</v>
+        <v>-0.3103</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8943</v>
+        <v>0.3139</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>1.1857</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5138</v>
+        <v>1.1857</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7425</v>
+        <v>-0.1475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07489999999999999</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8174</v>
+        <v>-0.1475</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.529</v>
+        <v>-0.207</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7668</v>
+        <v>-0.207</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7622</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8344</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0519</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7825</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6946</v>
+        <v>-0.207</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7149</v>
+        <v>-0.207</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9797</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.386</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7926</v>
+        <v>-0.1335</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1607</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6319</v>
+        <v>-0.1335</v>
       </c>
       <c r="V9" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4559</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3796</v>
+        <v>-1.2735</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2063</v>
+        <v>1.3659</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5858</v>
+        <v>-2.6394</v>
       </c>
       <c r="G10" t="n">
         <v>-1.9433</v>
@@ -1234,13 +1234,13 @@
         <v>0.965</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1428</v>
+        <v>0.2489</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1507</v>
+        <v>0.0089</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2934</v>
+        <v>0.2399</v>
       </c>
       <c r="V10" t="n">
         <v>0.614</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.4488</v>
+        <v>5.6387</v>
       </c>
       <c r="E11" t="n">
-        <v>6.8286</v>
+        <v>8.0183</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.379499999999999</v>
+        <v>-2.3797</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3002</v>
+        <v>0.3002000000000009</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3058</v>
+        <v>4.305800000000001</v>
       </c>
       <c r="I11" t="n">
         <v>-4.0056</v>
@@ -1312,13 +1312,13 @@
         <v>15.4406</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.6704</v>
+        <v>-1.4806</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5796</v>
+        <v>-0.3898999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0909</v>
+        <v>-1.0908</v>
       </c>
       <c r="V11" t="n">
         <v>5.854</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.9766</v>
+        <v>4.6134</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4147</v>
+        <v>5.4177</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4381</v>
+        <v>-0.8043</v>
       </c>
       <c r="G12" t="n">
-        <v>5.4467</v>
+        <v>3.6452</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5474</v>
+        <v>2.3442</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1007</v>
+        <v>1.3009</v>
       </c>
       <c r="J12" t="n">
-        <v>7.8426</v>
+        <v>4.773</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1101</v>
+        <v>3.4463</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7326</v>
+        <v>1.3267</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.396</v>
+        <v>-1.1278</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5627</v>
+        <v>-1.1021</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8333</v>
+        <v>-0.0257</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7371</v>
+        <v>0.965</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8951</v>
+        <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8231</v>
+        <v>1.2734</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8376</v>
+        <v>0.4241</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9855</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5561</v>
+        <v>-1.2702</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3704</v>
+        <v>1.1857</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1857</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.7809</v>
+        <v>3.5674</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3176</v>
+        <v>5.1129</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5366</v>
+        <v>-1.5455</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6452</v>
+        <v>5.4467</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3442</v>
+        <v>5.5474</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3009</v>
+        <v>-0.1007</v>
       </c>
       <c r="J13" t="n">
-        <v>4.773</v>
+        <v>7.8426</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4463</v>
+        <v>7.1101</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3267</v>
+        <v>0.7326</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1278</v>
+        <v>-2.396</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1021</v>
+        <v>-1.5627</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0257</v>
+        <v>-0.8333</v>
       </c>
       <c r="P13" t="n">
-        <v>0.965</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9301</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4409</v>
+        <v>1.4139</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3239</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.117</v>
+        <v>0.8781</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2702</v>
+        <v>-1.5561</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1857</v>
+        <v>-0.3704</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4559</v>
+        <v>-1.1857</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4819</v>
+        <v>1.5639</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2347</v>
+        <v>1.8355</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7528</v>
+        <v>-0.2716</v>
       </c>
       <c r="G14" t="n">
         <v>0.1124</v>
@@ -1546,13 +1546,13 @@
         <v>0.772</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7786</v>
+        <v>0.3034</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7139</v>
+        <v>-0.113</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0648</v>
+        <v>0.4164</v>
       </c>
       <c r="V14" t="n">
         <v>0.7621</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GARCIA NAVALON</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3032</v>
+        <v>1.0542</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2667</v>
+        <v>0.1517</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5699</v>
+        <v>0.9025</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3116</v>
+        <v>2.9149</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8795</v>
+        <v>2.2687</v>
       </c>
       <c r="I15" t="n">
-        <v>1.568</v>
+        <v>0.6462</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4584</v>
+        <v>4.5966</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.2317</v>
+        <v>4.0518</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7733</v>
+        <v>0.5448</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1469</v>
+        <v>-1.6817</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6478</v>
+        <v>-1.7831</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7947</v>
+        <v>0.1014</v>
       </c>
       <c r="P15" t="n">
-        <v>0.772</v>
+        <v>-0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.2811</v>
       </c>
       <c r="R15" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1573</v>
+        <v>-0.0595</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1917</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.349</v>
+        <v>0.4481</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. GARCIA NAVALON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0089</v>
+        <v>0.6571</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7692</v>
+        <v>0.0337</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7602</v>
+        <v>0.6234</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3928</v>
+        <v>-0.3116</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.502</v>
+        <v>-1.8795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1092</v>
+        <v>1.568</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2195</v>
+        <v>-0.4584</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3416</v>
+        <v>-1.2317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1221</v>
+        <v>0.7733</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1732</v>
+        <v>0.1469</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1604</v>
+        <v>-0.6478</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0129</v>
+        <v>0.7947</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1607</v>
+        <v>0.1966</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9188</v>
+        <v>0.4921</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2419</v>
+        <v>-0.2955</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1211</v>
+        <v>-0.3986</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6495</v>
+        <v>0.4687</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5284</v>
+        <v>-0.8673</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9149</v>
+        <v>-0.3928</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2687</v>
+        <v>-0.502</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6462</v>
+        <v>0.1092</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5966</v>
+        <v>-0.2195</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0518</v>
+        <v>-0.3416</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5448</v>
+        <v>0.1221</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6817</v>
+        <v>-0.1732</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7831</v>
+        <v>-0.1604</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1014</v>
+        <v>-0.0129</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.965</v>
+        <v>-0.579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2811</v>
+        <v>-1.158</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3161</v>
+        <v>0.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2347</v>
+        <v>0.7532</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3087</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.074</v>
+        <v>0.1348</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.18</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6562</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.18</v>
+        <v>-1.4079</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0939</v>
+        <v>-1.1742</v>
       </c>
       <c r="E18" t="n">
         <v>-0.9838</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.11</v>
+        <v>-0.1903</v>
       </c>
       <c r="G18" t="n">
         <v>0.0873</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2162</v>
+        <v>-0.2965</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1567</v>
+        <v>-0.237</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7828</v>
+        <v>-2.1396</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0249</v>
+        <v>-1.0235</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7579</v>
+        <v>-1.1161</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5166</v>
@@ -1936,13 +1936,13 @@
         <v>2.7021</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3491</v>
+        <v>-0.7059</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6062</v>
+        <v>-0.6048</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.743</v>
+        <v>-0.1012</v>
       </c>
       <c r="V19" t="n">
         <v>1.662</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8596</v>
+        <v>-4.127</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5924</v>
+        <v>-2.9929</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2672</v>
+        <v>-1.134</v>
       </c>
       <c r="G20" t="n">
         <v>-3.22</v>
@@ -2014,13 +2014,13 @@
         <v>2.5091</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8163</v>
+        <v>0.549</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.1745</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2412</v>
+        <v>0.3744</v>
       </c>
       <c r="V20" t="n">
         <v>-1.842</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1431</v>
+        <v>-6.7304</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8393</v>
+        <v>-5.6404</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3038</v>
+        <v>-1.09</v>
       </c>
       <c r="G21" t="n">
         <v>-6.0658</v>
@@ -2092,13 +2092,13 @@
         <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1653</v>
+        <v>0.578</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.1309</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2333</v>
+        <v>0.4471</v>
       </c>
       <c r="V21" t="n">
         <v>-2.5937</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.448999999999998</v>
+        <v>-3.113799999999999</v>
       </c>
       <c r="E22" t="n">
         <v>2.3796</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.8283</v>
+        <v>-5.4932</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3003000000000009</v>
+        <v>-0.3003000000000027</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.305800000000001</v>
+        <v>-4.3058</v>
       </c>
       <c r="I22" t="n">
         <v>4.005500000000001</v>
@@ -2170,13 +2170,13 @@
         <v>14.4755</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6704</v>
+        <v>4.0056</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0908</v>
+        <v>1.0909</v>
       </c>
       <c r="U22" t="n">
-        <v>1.5794</v>
+        <v>2.9145</v>
       </c>
       <c r="V22" t="n">
         <v>-5.8541</v>
